--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,9 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R3d141859b0024e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R21738b0c863544f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="3" r:id="R1453db7b33654cb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R703fac78f1b04d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R8508f37d86fd4c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R16d309fa60744260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R006e43e6dd014042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R15d0ededeed142d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="6" r:id="R7d7096cd37d645d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -60,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -88,6 +94,7 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -394,13 +401,14 @@
   <x:cols>
     <x:col min="1" max="1" width="9.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="5.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.109999656677246" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -411,24 +419,27 @@
         <x:v>specialty_code</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
         <x:v>course</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>education_form</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>headcount</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>program_base</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>study_week_type</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>primary_building_code</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>subgroup_count</x:v>
       </x:c>
     </x:row>
@@ -439,25 +450,28 @@
       <x:c r="B2" s="7" t="str">
         <x:v>09.02.07</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="n">
+      <x:c r="C2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
+      <x:c r="E2" s="7" t="str">
         <x:v>full_time</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="n">
+      <x:c r="F2" s="7" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F2" s="7" t="str">
+      <x:c r="G2" s="7" t="str">
         <x:v>9_classes</x:v>
       </x:c>
-      <x:c r="G2" s="7" t="str">
+      <x:c r="H2" s="7" t="str">
         <x:v>six_days</x:v>
       </x:c>
-      <x:c r="H2" s="7" t="str">
+      <x:c r="I2" s="7" t="str">
         <x:v>MAIN</x:v>
       </x:c>
-      <x:c r="I2" s="7" t="n">
+      <x:c r="J2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -467,6 +481,196 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38.11000061035156" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34.11000061035156" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>specialty_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>specialty_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>qualification</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>program_base</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>education_form</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>09.02.07</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Информационные системы и программирование</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Специалист по информационным системам</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>full_time</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.329999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>specialty_code</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>admission_year</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>valid_from</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>valid_to</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>09.02.07</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.4399995803833" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>curriculum_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>discipline_code</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>discipline_name</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>section_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>semester</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>lesson_type</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>planned_hours</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>control_form</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>UP-09.02.07-2026</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>MDK.01.01</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Основы программирования</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>ПМ.01</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>practice</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>credit</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R703fac78f1b04d1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R8508f37d86fd4c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R16d309fa60744260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R006e43e6dd014042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R15d0ededeed142d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="6" r:id="R7d7096cd37d645d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R8175026a282145bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R0e330eb8e8254921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R96b50963fa3f4f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rc0c7004407a24a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R164ea83ddf7a4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R03691ae255264055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="7" r:id="R87899c9f3b6c4100"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,6 +675,75 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="5.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>student_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>full_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>group_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>enrollment_date</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>end_date</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>subgroup_codes</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>elective_codes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>S-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Петров Пётр Петрович</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>ИС-101</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>WEB</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,13 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R8175026a282145bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R0e330eb8e8254921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R96b50963fa3f4f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rc0c7004407a24a56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R164ea83ddf7a4040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R03691ae255264055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="7" r:id="R87899c9f3b6c4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R5e5cdd77dda64a54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R1eefb5e962744949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R15b9ef57eda249a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R4bafd4599d374e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R37f6ee7eea534420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Rb82e7459e4154b9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="Rbf14ef6758144534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R4ff8059036924bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rc506d9767ce24ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Re99e77696c034df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rab84c7bf239947aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -396,6 +400,198 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>room_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>room_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>building_code</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>room_type_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>equipment_codes</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>MAIN-201</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Лаборатория 201</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>MAIN</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>COMPUTER_LAB</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21.559999465942383" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>workload_row_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>academic_year</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>semester</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>discipline_code</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>discipline_name</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>group_code</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>subgroup</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>stream</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>teacher_code</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>lesson_type</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>total_academic_hours</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>event_duration_hours</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>recurrence</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>lesson_bundle_code</x:v>
+      </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>room_type</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>room_capacity</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>required_equipment_codes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>W-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>MDK.01.01</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>Основы программирования</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>ИС-101</x:v>
+      </x:c>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7" t="str">
+        <x:v>T-001</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="str">
+        <x:v>practice</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L2" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="str">
+        <x:v>weekly</x:v>
+      </x:c>
+      <x:c r="N2" s="7"/>
+      <x:c r="O2" s="7" t="str">
+        <x:v>computer_lab</x:v>
+      </x:c>
+      <x:c r="P2" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -744,116 +940,103 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>workload_row_code</x:v>
+        <x:v>building_code</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>academic_year</x:v>
+        <x:v>building_name</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>semester</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>discipline_code</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
-        <x:v>discipline_name</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="str">
-        <x:v>group_code</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>subgroup</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>stream</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>teacher_code</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>lesson_type</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>total_academic_hours</x:v>
-      </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>event_duration_hours</x:v>
-      </x:c>
-      <x:c r="M1" s="6" t="str">
-        <x:v>recurrence</x:v>
-      </x:c>
-      <x:c r="N1" s="6" t="str">
-        <x:v>lesson_bundle_code</x:v>
-      </x:c>
-      <x:c r="O1" s="6" t="str">
-        <x:v>room_type</x:v>
-      </x:c>
-      <x:c r="P1" s="6" t="str">
-        <x:v>room_capacity</x:v>
+        <x:v>active</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>W-001</x:v>
+        <x:v>MAIN</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026/2027</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="n">
+        <x:v>Главный корпус</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>MDK.01.01</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>Основы программирования</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="str">
-        <x:v>ИС-101</x:v>
-      </x:c>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7" t="str">
-        <x:v>T-001</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="str">
-        <x:v>practice</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L2" s="7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M2" s="7" t="str">
-        <x:v>weekly</x:v>
-      </x:c>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7" t="str">
-        <x:v>computer_lab</x:v>
-      </x:c>
-      <x:c r="P2" s="7" t="n">
-        <x:v>25</x:v>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>room_type_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>room_type_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>COMPUTER_LAB</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Компьютерный класс</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>equipment_code</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>equipment_name</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>COMPUTERS</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Компьютеры</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R5e5cdd77dda64a54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R1eefb5e962744949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R15b9ef57eda249a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R4bafd4599d374e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R37f6ee7eea534420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="Rb82e7459e4154b9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="Rbf14ef6758144534"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R4ff8059036924bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rc506d9767ce24ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Re99e77696c034df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rab84c7bf239947aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Rf14e943485d94d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R716045d7c7064409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rf11e7cb3d7db43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R3df7b957f08a4860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R26ba81ed96cb4173"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R89eefe7f65294be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="Redad93a6e71d4280"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R831ea4782b924c07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R418c1a4d5fa64778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Red4c3db40c6b466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R2da325fd85bc410d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,48 +319,48 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20.110000610351562" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="23.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>teacher_code</x:v>
+        <x:v>Код преподавателя</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>full_name</x:v>
+        <x:v>ФИО</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>department</x:v>
+        <x:v>Подразделение</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>employment_type</x:v>
+        <x:v>Тип занятости</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>yearly_assigned_hours</x:v>
+        <x:v>Назначено часов в год</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>yearly_limit_hours</x:v>
+        <x:v>Лимит часов в год</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>max_hours_per_day</x:v>
+        <x:v>Макс. часов в день</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>max_days_per_week</x:v>
+        <x:v>Макс. дней в неделю</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>home_building_code</x:v>
+        <x:v>Основной корпус</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -404,36 +404,36 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="7.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>room_code</x:v>
+        <x:v>Код аудитории</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>room_name</x:v>
+        <x:v>Название аудитории</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>building_code</x:v>
+        <x:v>Код корпуса</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>room_type_code</x:v>
+        <x:v>Код типа помещения</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>capacity</x:v>
+        <x:v>Вместимость</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>equipment_codes</x:v>
+        <x:v>Коды оборудования</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активна</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -468,76 +468,76 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="7.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="21.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="5.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21.329999923706055" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>workload_row_code</x:v>
+        <x:v>Код строки нагрузки</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>academic_year</x:v>
+        <x:v>Учебный год</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>semester</x:v>
+        <x:v>Семестр</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>discipline_code</x:v>
+        <x:v>Код дисциплины</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>discipline_name</x:v>
+        <x:v>Название дисциплины</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>subgroup</x:v>
+        <x:v>Подгруппа</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>stream</x:v>
+        <x:v>Поток</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>teacher_code</x:v>
+        <x:v>Код преподавателя</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>lesson_type</x:v>
+        <x:v>Вид занятия</x:v>
       </x:c>
       <x:c r="K1" s="6" t="str">
-        <x:v>total_academic_hours</x:v>
+        <x:v>Всего академических часов</x:v>
       </x:c>
       <x:c r="L1" s="6" t="str">
-        <x:v>event_duration_hours</x:v>
+        <x:v>Продолжительность занятия</x:v>
       </x:c>
       <x:c r="M1" s="6" t="str">
-        <x:v>recurrence</x:v>
+        <x:v>Периодичность</x:v>
       </x:c>
       <x:c r="N1" s="6" t="str">
-        <x:v>lesson_bundle_code</x:v>
+        <x:v>Код связки занятий</x:v>
       </x:c>
       <x:c r="O1" s="6" t="str">
-        <x:v>room_type</x:v>
+        <x:v>Тип помещения</x:v>
       </x:c>
       <x:c r="P1" s="6" t="str">
-        <x:v>room_capacity</x:v>
+        <x:v>Требуемая вместимость</x:v>
       </x:c>
       <x:c r="Q1" s="6" t="str">
-        <x:v>required_equipment_codes</x:v>
+        <x:v>Требуемое оборудование</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -596,48 +596,48 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="5.889999866485596" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.110000610351562" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>course</x:v>
+        <x:v>Курс</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>education_form</x:v>
+        <x:v>Форма обучения</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>headcount</x:v>
+        <x:v>Численность</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>program_base</x:v>
+        <x:v>База обучения</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>study_week_type</x:v>
+        <x:v>Тип учебной недели</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>primary_building_code</x:v>
+        <x:v>Основной корпус</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>subgroup_count</x:v>
+        <x:v>Количество подгрупп</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -681,32 +681,32 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="38.11000061035156" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34.11000061035156" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_name</x:v>
+        <x:v>Название специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>qualification</x:v>
+        <x:v>Квалификация</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>program_base</x:v>
+        <x:v>База обучения</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>education_form</x:v>
+        <x:v>Форма обучения</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активна</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -738,36 +738,36 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="6.21999979019165" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.559999942779541" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.110000133514404" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>specialty_code</x:v>
+        <x:v>Код специальности</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>admission_year</x:v>
+        <x:v>Год набора</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>version</x:v>
+        <x:v>Версия</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>valid_from</x:v>
+        <x:v>Действует с</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>valid_to</x:v>
+        <x:v>Действует по</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>status</x:v>
+        <x:v>Статус</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -800,40 +800,40 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="21.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.220000267028809" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>curriculum_code</x:v>
+        <x:v>Код учебного плана</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>discipline_code</x:v>
+        <x:v>Код дисциплины</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>discipline_name</x:v>
+        <x:v>Название дисциплины</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>section_code</x:v>
+        <x:v>Код раздела</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>semester</x:v>
+        <x:v>Семестр</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>lesson_type</x:v>
+        <x:v>Вид занятия</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>planned_hours</x:v>
+        <x:v>Плановые часы</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>control_form</x:v>
+        <x:v>Форма контроля</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -871,40 +871,40 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="5.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.890000343322754" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>student_code</x:v>
+        <x:v>Код студента</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>full_name</x:v>
+        <x:v>ФИО</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>group_code</x:v>
+        <x:v>Код группы</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>status</x:v>
+        <x:v>Статус</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>enrollment_date</x:v>
+        <x:v>Дата зачисления</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>end_date</x:v>
+        <x:v>Дата окончания</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>subgroup_codes</x:v>
+        <x:v>Номера подгрупп</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>elective_codes</x:v>
+        <x:v>Коды элективов</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -940,20 +940,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>building_code</x:v>
+        <x:v>Код корпуса</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>building_name</x:v>
+        <x:v>Название корпуса</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -976,20 +976,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.110000610351562" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>room_type_code</x:v>
+        <x:v>Код типа помещения</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>room_type_name</x:v>
+        <x:v>Название типа помещения</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активен</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1012,20 +1012,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.21999979019165" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>equipment_code</x:v>
+        <x:v>Код оборудования</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>equipment_name</x:v>
+        <x:v>Название оборудования</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>active</x:v>
+        <x:v>Активно</x:v>
       </x:c>
     </x:row>
     <x:row r="2">

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,17 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Rf14e943485d94d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R716045d7c7064409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rf11e7cb3d7db43c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R3df7b957f08a4860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R26ba81ed96cb4173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R89eefe7f65294be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="Redad93a6e71d4280"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R831ea4782b924c07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="R418c1a4d5fa64778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Red4c3db40c6b466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R2da325fd85bc410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Rfad6537c2bee447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R4af125b0ee9f47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R79f6bdad99834ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rdc81bfc2abf04ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R74d7aba234f5482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R3c9b3885d64e4fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R5c30d3793af844e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R99064fc6ff904cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rdccf73c7637a4b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R2c0473555ba1487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R4cbef38b9536409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="R6384ed0e3e004e4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rc8acedcfd0124fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="R1e8eb135a586468d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -592,6 +595,170 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.21999979019165" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Активен</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="n">
+        <x:v>46568</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.559999942779541" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код периода</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Название периода</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Тип периода</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Семестр</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>SEM-1</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Первый семестр</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>teaching</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>46384</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.4399995803833" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код интервала</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Код смены</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Номер занятия</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Начало</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Окончание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>S1-01</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>S1</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>08:30</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>10:00</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,20 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="Rfad6537c2bee447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="R4af125b0ee9f47bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R79f6bdad99834ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="Rdc81bfc2abf04ffd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R74d7aba234f5482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R3c9b3885d64e4fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R5c30d3793af844e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R99064fc6ff904cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rdccf73c7637a4b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="R2c0473555ba1487b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R4cbef38b9536409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="R6384ed0e3e004e4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rc8acedcfd0124fdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="R1e8eb135a586468d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R298bbcd241444a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rb9c5e8f255834d54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rf29756a6b30648ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R2a35b82280a045cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R61de88e4ba2f44fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R0856290a12784082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R9bebf47362324b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R733679b184f242f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rb26bb81cac184fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Rb6819757049a4ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rb3ae5ef4c76c47c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="R55360ef186454741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rec23729a3d594cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Rc1c507fb2a204868"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="15" r:id="R0cb4c73523894c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="16" r:id="R8328df5e02e94d09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -759,6 +761,140 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.440000534057617" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код исключения</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Тип исключения</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Дата исключения</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Перенос на дату</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Сокращённый день до</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Примечание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>EX-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>holiday</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>46330</x:v>
+      </x:c>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="7"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>День народного единства</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.110000610351562" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код недоступности</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Тип ресурса</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Код ресурса</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Дата окончания</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Время начала</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Время окончания</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Причина</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>U-001</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>teacher</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>T-001</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7" t="str">
+        <x:v>Повышение квалификации</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/tests/fixtures/valid-import.xlsx
+++ b/tests/fixtures/valid-import.xlsx
@@ -2,22 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R298bbcd241444a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rb9c5e8f255834d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="Rf29756a6b30648ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R2a35b82280a045cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R61de88e4ba2f44fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R0856290a12784082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="R9bebf47362324b60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R733679b184f242f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Rb26bb81cac184fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Rb6819757049a4ffd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="Rb3ae5ef4c76c47c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="R55360ef186454741"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="13" r:id="Rec23729a3d594cd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="14" r:id="Rc1c507fb2a204868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="15" r:id="R0cb4c73523894c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="16" r:id="R8328df5e02e94d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Преподаватели" sheetId="1" r:id="R6cddd15c2ec94ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" r:id="Rf805483e46774d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Специальности" sheetId="3" r:id="R1186e4e4e56a46e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные планы" sheetId="4" r:id="R7441e51292d74df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дисциплины" sheetId="5" r:id="R67c8d7cc7bd44163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Студенты" sheetId="6" r:id="R85b3d6a9c77a42a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Корпуса" sheetId="7" r:id="Rb5da60cbd37744f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы помещений" sheetId="8" r:id="R95aeb5400e8b4a11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="9" r:id="Raf1287d8c10e4612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудитории" sheetId="10" r:id="Rf2807341468c4db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузка" sheetId="11" r:id="R63436975e3784400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные годы" sheetId="12" r:id="Rf8277d999d6a4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Учебные циклы" sheetId="13" r:id="R4ff3c5256b4b4f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Периоды" sheetId="14" r:id="Rd9cb557daf224b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сетка звонков" sheetId="15" r:id="Rde658bafd07448eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исключения календаря" sheetId="16" r:id="Rc297c51991ca4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Недоступность" sheetId="17" r:id="R6d48c4c628c54ced"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -490,6 +491,8 @@
     <x:col min="15" max="15" width="13.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="21.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="23" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18.219999313354492" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -543,6 +546,12 @@
       </x:c>
       <x:c r="Q1" s="6" t="str">
         <x:v>Требуемое оборудование</x:v>
+      </x:c>
+      <x:c r="R1" s="6" t="str">
+        <x:v>Код учебного цикла</x:v>
+      </x:c>
+      <x:c r="S1" s="6" t="str">
+        <x:v>Номера недель цикла</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -591,6 +600,12 @@
       <x:c r="Q2" s="7" t="str">
         <x:v>COMPUTERS</x:v>
       </x:c>
+      <x:c r="R2" s="7" t="str">
+        <x:v>NUMERATOR-DENOMINATOR</x:v>
+      </x:c>
+      <x:c r="S2" s="7" t="str">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -641,6 +656,63 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.21999979019165" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Код цикла</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Учебный год</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Название цикла</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Длина цикла в неделях</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Дата начала отсчёта</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Активен</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>NUMERATOR-DENOMINATOR</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>2026/2027</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Числитель / знаменатель</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -704,7 +776,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -761,7 +833,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -821,7 +893,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
